--- a/data/trans_orig/CAGE_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2007</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682070</t>
+          <t>682132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692949</t>
+          <t>692300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>686455</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688351</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1371052</t>
+          <t>1371055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1381302</t>
+          <t>1381307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>947589</t>
+          <t>947902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>958717</t>
+          <t>958819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>961583</t>
+          <t>962631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1914873</t>
+          <t>1914339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1926310</t>
+          <t>1926274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665750</t>
+          <t>665251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675644</t>
+          <t>675796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>681957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>683841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1349173</t>
+          <t>1347850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1359452</t>
+          <t>1359413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927125</t>
+          <t>926965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>939232</t>
+          <t>938958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1021437</t>
+          <t>1021858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034964</t>
+          <t>1034921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1954815</t>
+          <t>1954693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972039</t>
+          <t>1972257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +2155,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>24204</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>47707</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>24809</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>48344</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3237641</t>
+          <t>3238497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3259498</t>
+          <t>3259529</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3361538</t>
+          <t>3360830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3375477</t>
+          <t>3374871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +2268,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6608034</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6631537</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6607397</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6630932</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2012</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>16329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16895</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>688236</t>
+          <t>687140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>699120</t>
+          <t>698868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>692002</t>
+          <t>691872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1383624</t>
+          <t>1383550</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1395417</t>
+          <t>1395525</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>991578</t>
+          <t>989723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010671</t>
+          <t>1010926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1027231</t>
+          <t>1026197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2023640</t>
+          <t>2022821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2041839</t>
+          <t>2041887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29002</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29383</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>728621</t>
+          <t>728182</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>746946</t>
+          <t>746857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>771968</t>
+          <t>772175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505414</t>
+          <t>1504579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523537</t>
+          <t>1522840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>909587</t>
+          <t>909012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931442</t>
+          <t>931559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1044297</t>
+          <t>1044431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1959221</t>
+          <t>1958564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1982266</t>
+          <t>1981043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85946</t>
+          <t>84334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91422</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3340833</t>
+          <t>3342445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3376500</t>
+          <t>3376774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3546904</t>
+          <t>3546864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3556323</t>
+          <t>3556320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6893666</t>
+          <t>6895004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6929953</t>
+          <t>6929706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2016</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672215</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>666262</t>
+          <t>666206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331916</t>
+          <t>1331418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343636</t>
+          <t>1344156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39102</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>987525</t>
+          <t>987396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008568</t>
+          <t>1008594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1034839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1041986</t>
+          <t>1041980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2026242</t>
+          <t>2026745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049624</t>
+          <t>2048977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744699</t>
+          <t>744248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756340</t>
+          <t>756333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>782966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>785011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1529518</t>
+          <t>1529661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1541428</t>
+          <t>1541397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35202</t>
+          <t>35675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917277</t>
+          <t>916908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>930653</t>
+          <t>931231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1023995</t>
+          <t>1023328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037683</t>
+          <t>1037838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946144</t>
+          <t>1945671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966375</t>
+          <t>1966878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65896</t>
+          <t>65692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85316</t>
+          <t>83590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3328454</t>
+          <t>3328658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3357958</t>
+          <t>3358339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3516511</t>
+          <t>3517413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3534797</t>
+          <t>3534672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6853576</t>
+          <t>6855302</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6887541</t>
+          <t>6888494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2023</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325515</t>
+          <t>325445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>331707</t>
+          <t>331717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155105</t>
+          <t>155183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484121</t>
+          <t>483841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>490916</t>
+          <t>491118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>459604</t>
+          <t>459366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471937</t>
+          <t>472040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188597</t>
+          <t>188617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>197817</t>
+          <t>198000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652465</t>
+          <t>652555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>667669</t>
+          <t>667704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309778</t>
+          <t>309297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318963</t>
+          <t>318919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353634</t>
+          <t>353982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669348</t>
+          <t>670376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687049</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>28242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>414874</t>
+          <t>414432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432525</t>
+          <t>432379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282360</t>
+          <t>281716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287642</t>
+          <t>287846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>699639</t>
+          <t>700214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719030</t>
+          <t>718838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>50138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64109</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1524803</t>
+          <t>1523399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1548782</t>
+          <t>1547632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>994878</t>
+          <t>993489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1011772</t>
+          <t>1011904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2526989</t>
+          <t>2526518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2556512</t>
+          <t>2558404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682132</t>
+          <t>681538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692300</t>
+          <t>692954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1371055</t>
+          <t>1369633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1381307</t>
+          <t>1381303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>947902</t>
+          <t>947672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>958819</t>
+          <t>958833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>962631</t>
+          <t>962583</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1914339</t>
+          <t>1915080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1926274</t>
+          <t>1926606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665251</t>
+          <t>665732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675796</t>
+          <t>675837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1347850</t>
+          <t>1348982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1359413</t>
+          <t>1359559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>25547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926965</t>
+          <t>926789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>938958</t>
+          <t>938826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1021858</t>
+          <t>1021629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034921</t>
+          <t>1035396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1954693</t>
+          <t>1955287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972257</t>
+          <t>1972241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4632</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18511</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>24974</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>48973</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9289</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>18367</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>24204</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>47707</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,77 +2238,77 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>687140</t>
+          <t>687887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>698868</t>
+          <t>699182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>691872</t>
+          <t>691994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1383550</t>
+          <t>1382737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1395525</t>
+          <t>1395454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>989723</t>
+          <t>992156</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010926</t>
+          <t>1011364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1026197</t>
+          <t>1027285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2022821</t>
+          <t>2022244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2041887</t>
+          <t>2042690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>28853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>728182</t>
+          <t>728770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>746857</t>
+          <t>746674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>772175</t>
+          <t>772145</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504579</t>
+          <t>1504236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1522840</t>
+          <t>1522763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>40765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>909012</t>
+          <t>909475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931559</t>
+          <t>931563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1044431</t>
+          <t>1044952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1958564</t>
+          <t>1958875</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1981043</t>
+          <t>1981543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50005</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84334</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90084</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3342445</t>
+          <t>3341906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3376774</t>
+          <t>3377081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3546864</t>
+          <t>3546084</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3556320</t>
+          <t>3556330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6895004</t>
+          <t>6894514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6929706</t>
+          <t>6929568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>660263</t>
+          <t>661615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671731</t>
+          <t>672404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>666206</t>
+          <t>666528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331418</t>
+          <t>1331114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1344156</t>
+          <t>1343956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35035</t>
+          <t>34870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>15760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38599</t>
+          <t>37583</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>987396</t>
+          <t>987561</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008594</t>
+          <t>1008207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1034839</t>
+          <t>1034314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1041980</t>
+          <t>1041985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2026745</t>
+          <t>2027761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2048977</t>
+          <t>2049584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744248</t>
+          <t>745421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756333</t>
+          <t>756330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1529661</t>
+          <t>1529592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1541397</t>
+          <t>1541390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916908</t>
+          <t>916771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931231</t>
+          <t>930757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1023328</t>
+          <t>1023090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037838</t>
+          <t>1037793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945671</t>
+          <t>1944846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966878</t>
+          <t>1965414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65692</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50398</t>
+          <t>51207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>83935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3328658</t>
+          <t>3330290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3358339</t>
+          <t>3358349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3517413</t>
+          <t>3518342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3534672</t>
+          <t>3535282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6855302</t>
+          <t>6854957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6888494</t>
+          <t>6887685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>329649</t>
+          <t>349946</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325445</t>
+          <t>346041</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>331717</t>
+          <t>351941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,27 +6717,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>158790</t>
+          <t>171764</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155183</t>
+          <t>168387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>488439</t>
+          <t>521710</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>483841</t>
+          <t>517292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>491118</t>
+          <t>524324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>23866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>467278</t>
+          <t>491304</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>459366</t>
+          <t>483991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472040</t>
+          <t>496521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>194703</t>
+          <t>216117</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188617</t>
+          <t>209150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198000</t>
+          <t>219293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>661980</t>
+          <t>707423</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652555</t>
+          <t>698671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>667704</t>
+          <t>713601</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200071</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200071</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200071</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>676827</t>
+          <t>722537</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>676827</t>
+          <t>722537</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>676827</t>
+          <t>722537</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>24712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>315852</t>
+          <t>345294</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309297</t>
+          <t>335645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318919</t>
+          <t>350588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>364852</t>
+          <t>189256</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353982</t>
+          <t>178161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>192205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>680705</t>
+          <t>534549</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670376</t>
+          <t>523777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>540977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>29144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31318</t>
+          <t>37304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>425453</t>
+          <t>445547</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>414432</t>
+          <t>435379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432379</t>
+          <t>453727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>285856</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281716</t>
+          <t>294380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287846</t>
+          <t>305832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>711309</t>
+          <t>748089</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700214</t>
+          <t>735062</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718838</t>
+          <t>757173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>74386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1538231</t>
+          <t>1632092</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1523399</t>
+          <t>1617778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1547632</t>
+          <t>1643478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1004202</t>
+          <t>879679</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>993489</t>
+          <t>867843</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1011904</t>
+          <t>886578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2542434</t>
+          <t>2511770</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2526518</t>
+          <t>2495242</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2558404</t>
+          <t>2525557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
